--- a/data/eval/drilling_station.xlsx
+++ b/data/eval/drilling_station.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gmasso16/Documents/Enseignement_new/Cours/Fiabilité/Projets/Rotary drilling machine/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492F235B-5880-0049-9832-E8934ED5D8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A752E1CB-0D22-8E4C-B25B-FAD89F537729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="1900" windowWidth="25820" windowHeight="16180" activeTab="5" xr2:uid="{7F048A70-FEF9-994F-9A54-B41F804C0326}"/>
+    <workbookView xWindow="15660" yWindow="-28200" windowWidth="34400" windowHeight="28200" activeTab="5" xr2:uid="{7F048A70-FEF9-994F-9A54-B41F804C0326}"/>
   </bookViews>
   <sheets>
     <sheet name="rotating_platform" sheetId="2" r:id="rId1"/>
@@ -70,13 +70,13 @@
     <t>7</t>
   </si>
   <si>
-    <t>nb-partialcleaning</t>
+    <t>nbHours</t>
   </si>
   <si>
-    <t>fullcleaning-duration</t>
+    <t>nb_partialcleaning</t>
   </si>
   <si>
-    <t>nbHours</t>
+    <t>fullcleaning_duration</t>
   </si>
 </sst>
 </file>
@@ -896,3430 +896,2977 @@
         <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>685</v>
+        <v>3033</v>
       </c>
       <c r="B2">
-        <v>5452</v>
+        <v>4804</v>
       </c>
       <c r="C2">
-        <v>10921</v>
+        <v>7026</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2">
-        <v>4.3099999999999996</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>2681</v>
-      </c>
-      <c r="B3">
-        <v>7844</v>
-      </c>
-      <c r="C3">
-        <v>18325</v>
+        <v>4985</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2.65</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>6120</v>
-      </c>
-      <c r="B4">
-        <v>13833</v>
+        <v>1137</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>3.25</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>10392</v>
+        <v>6134</v>
+      </c>
+      <c r="B5">
+        <v>7268</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>6.04</v>
+        <v>4.0599999999999996</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>15200</v>
+        <v>4929</v>
+      </c>
+      <c r="B6">
+        <v>7518</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>4.33</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>829</v>
+        <v>6404</v>
       </c>
       <c r="B7">
-        <v>9854</v>
+        <v>6458</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7">
-        <v>8.08</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>6002</v>
+        <v>3239</v>
       </c>
       <c r="B8">
-        <v>9826</v>
+        <v>4725</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8">
-        <v>4.91</v>
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>2962</v>
+        <v>5478</v>
       </c>
       <c r="B9">
-        <v>4776</v>
+        <v>6858</v>
       </c>
       <c r="C9">
-        <v>4999</v>
-      </c>
-      <c r="D9">
-        <v>8124</v>
-      </c>
-      <c r="E9">
-        <v>10176</v>
+        <v>8532</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>3.92</v>
+        <v>4.8899999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>2237</v>
+        <v>900</v>
       </c>
       <c r="B10">
-        <v>6176</v>
-      </c>
-      <c r="C10">
-        <v>9832</v>
+        <v>7106</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>3.27</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>5931</v>
+        <v>4150</v>
       </c>
       <c r="B11">
-        <v>5934</v>
+        <v>5160</v>
       </c>
       <c r="C11">
-        <v>5973</v>
+        <v>7758</v>
       </c>
       <c r="D11">
-        <v>13267</v>
+        <v>7872</v>
       </c>
       <c r="H11">
         <v>4</v>
       </c>
       <c r="I11">
-        <v>6.96</v>
+        <v>5.0599999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>16233</v>
+        <v>6335</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>5.47</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>3969</v>
+        <v>4579</v>
       </c>
       <c r="B13">
-        <v>5322</v>
-      </c>
-      <c r="C13">
-        <v>18819</v>
+        <v>5491</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>5.01</v>
+        <v>4.7699999999999996</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>2416</v>
+        <v>2672</v>
       </c>
       <c r="B14">
-        <v>9399</v>
+        <v>4055</v>
+      </c>
+      <c r="C14">
+        <v>7369</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>4.7300000000000004</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>10841</v>
+        <v>1052</v>
+      </c>
+      <c r="B15">
+        <v>2396</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>4.47</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>1022</v>
+        <v>3914</v>
       </c>
       <c r="B16">
-        <v>6251</v>
-      </c>
-      <c r="C16">
-        <v>7346</v>
-      </c>
-      <c r="D16">
-        <v>7829</v>
-      </c>
-      <c r="E16">
-        <v>9037</v>
+        <v>8637</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>3965</v>
-      </c>
-      <c r="B17">
-        <v>4643</v>
-      </c>
-      <c r="C17">
-        <v>11032</v>
+        <v>6828</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>5.03</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>6236</v>
+        <v>6396</v>
       </c>
       <c r="B18">
-        <v>12023</v>
+        <v>8068</v>
       </c>
       <c r="H18">
         <v>2</v>
       </c>
       <c r="I18">
-        <v>4.2</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>3149</v>
+        <v>4981</v>
       </c>
       <c r="B19">
-        <v>4695</v>
-      </c>
-      <c r="C19">
-        <v>5011</v>
-      </c>
-      <c r="D19">
-        <v>8933</v>
+        <v>7401</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>2.5499999999999998</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>6777</v>
+        <v>3341</v>
       </c>
       <c r="B20">
-        <v>8572</v>
+        <v>5308</v>
       </c>
       <c r="C20">
-        <v>12228</v>
+        <v>6731</v>
+      </c>
+      <c r="D20">
+        <v>8092</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>3.44</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>3754</v>
-      </c>
-      <c r="B21">
-        <v>9959</v>
+        <v>7584</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>5.67</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>11334</v>
+        <v>5425</v>
+      </c>
+      <c r="B22">
+        <v>6789</v>
+      </c>
+      <c r="C22">
+        <v>8521</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <v>4.38</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>5817</v>
+        <v>1971</v>
       </c>
       <c r="B23">
-        <v>13432</v>
+        <v>2536</v>
+      </c>
+      <c r="C23">
+        <v>8195</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>3.82</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>685</v>
+        <v>2702</v>
       </c>
       <c r="B24">
-        <v>5385</v>
+        <v>3047</v>
       </c>
       <c r="C24">
-        <v>6173</v>
-      </c>
-      <c r="D24">
-        <v>9694</v>
+        <v>6493</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I24">
-        <v>4.7699999999999996</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>1768</v>
-      </c>
-      <c r="B25">
-        <v>5738</v>
-      </c>
-      <c r="C25">
-        <v>14781</v>
+        <v>4151</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>1204</v>
-      </c>
-      <c r="B26">
-        <v>5487</v>
-      </c>
-      <c r="C26">
-        <v>18585</v>
+        <v>7908</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>3.59</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>5059</v>
-      </c>
-      <c r="B27">
-        <v>6060</v>
-      </c>
-      <c r="C27">
-        <v>8900</v>
+        <v>1929</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>3.94</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>5046</v>
+        <v>2144</v>
       </c>
       <c r="B28">
-        <v>15426</v>
+        <v>3101</v>
+      </c>
+      <c r="C28">
+        <v>7319</v>
+      </c>
+      <c r="D28">
+        <v>8433</v>
+      </c>
+      <c r="E28">
+        <v>8576</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I28">
-        <v>6.87</v>
+        <v>4.1399999999999997</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>3265</v>
+        <v>1070</v>
       </c>
       <c r="B29">
-        <v>7656</v>
-      </c>
-      <c r="C29">
-        <v>9062</v>
+        <v>6255</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>2.4900000000000002</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>3575</v>
-      </c>
-      <c r="B30">
-        <v>9092</v>
+        <v>430</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>4.84</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>3629</v>
+        <v>542</v>
       </c>
       <c r="B31">
-        <v>4261</v>
+        <v>562</v>
       </c>
       <c r="C31">
-        <v>5886</v>
+        <v>5059</v>
       </c>
       <c r="D31">
-        <v>6259</v>
-      </c>
-      <c r="E31">
-        <v>12714</v>
+        <v>6992</v>
       </c>
       <c r="H31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I31">
-        <v>3.09</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>374</v>
+        <v>3944</v>
       </c>
       <c r="B32">
-        <v>2253</v>
-      </c>
-      <c r="C32">
-        <v>8013</v>
-      </c>
-      <c r="D32">
-        <v>21013</v>
+        <v>5468</v>
       </c>
       <c r="H32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>3.15</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>4809</v>
-      </c>
-      <c r="B33">
-        <v>9759</v>
+        <v>8931</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>3.5</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>387</v>
+        <v>2623</v>
       </c>
       <c r="B34">
-        <v>1209</v>
+        <v>2865</v>
       </c>
       <c r="C34">
-        <v>5288</v>
-      </c>
-      <c r="D34">
-        <v>9981</v>
+        <v>7491</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I34">
-        <v>6.42</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>4620</v>
-      </c>
-      <c r="B35">
-        <v>4919</v>
-      </c>
-      <c r="C35">
-        <v>9725</v>
+        <v>265</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>8119</v>
-      </c>
-      <c r="B36">
-        <v>11704</v>
+        <v>11110</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>5.37</v>
+        <v>2.2200000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>5727</v>
-      </c>
-      <c r="B37">
-        <v>5890</v>
-      </c>
-      <c r="C37">
-        <v>17583</v>
+        <v>4880</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>3.18</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>2437</v>
+        <v>5571</v>
       </c>
       <c r="B38">
-        <v>4780</v>
-      </c>
-      <c r="C38">
-        <v>9013</v>
+        <v>8277</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>3.72</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>6225</v>
+        <v>723</v>
       </c>
       <c r="B39">
-        <v>9795</v>
+        <v>4148</v>
+      </c>
+      <c r="C39">
+        <v>5898</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I39">
-        <v>4.8099999999999996</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>4726</v>
+        <v>1401</v>
       </c>
       <c r="B40">
-        <v>9648</v>
+        <v>1982</v>
+      </c>
+      <c r="C40">
+        <v>3051</v>
+      </c>
+      <c r="D40">
+        <v>6034</v>
+      </c>
+      <c r="E40">
+        <v>6922</v>
+      </c>
+      <c r="F40">
+        <v>7166</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I40">
-        <v>4.46</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>3475</v>
-      </c>
-      <c r="B41">
-        <v>7877</v>
-      </c>
-      <c r="C41">
-        <v>8446</v>
-      </c>
-      <c r="D41">
-        <v>11594</v>
+        <v>10222</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>6.57</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>9315</v>
+        <v>2064</v>
+      </c>
+      <c r="B42">
+        <v>3701</v>
+      </c>
+      <c r="C42">
+        <v>3784</v>
+      </c>
+      <c r="D42">
+        <v>7196</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I42">
-        <v>4.3499999999999996</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>7644</v>
-      </c>
-      <c r="B43">
-        <v>12050</v>
+        <v>11661</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>5.77</v>
+        <v>4.4400000000000004</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>2079</v>
+        <v>3533</v>
       </c>
       <c r="B44">
-        <v>10806</v>
+        <v>3554</v>
+      </c>
+      <c r="C44">
+        <v>7841</v>
+      </c>
+      <c r="D44">
+        <v>8158</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44">
-        <v>6.98</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>1247</v>
+        <v>2299</v>
       </c>
       <c r="B45">
-        <v>2248</v>
+        <v>6357</v>
       </c>
       <c r="C45">
-        <v>10688</v>
+        <v>8605</v>
       </c>
       <c r="H45">
         <v>3</v>
       </c>
       <c r="I45">
-        <v>6.69</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>974</v>
+        <v>6835</v>
       </c>
       <c r="B46">
-        <v>5758</v>
-      </c>
-      <c r="C46">
-        <v>11268</v>
+        <v>8671</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46">
-        <v>4.34</v>
+        <v>4.6500000000000004</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>7537</v>
-      </c>
-      <c r="B47">
-        <v>8429</v>
-      </c>
-      <c r="C47">
-        <v>10983</v>
+        <v>3934</v>
       </c>
       <c r="H47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>3240</v>
-      </c>
-      <c r="B48">
-        <v>11842</v>
+        <v>7928</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>4.5999999999999996</v>
+        <v>5.0599999999999996</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>241</v>
+        <v>1524</v>
       </c>
       <c r="B49">
-        <v>4083</v>
-      </c>
-      <c r="C49">
-        <v>5821</v>
-      </c>
-      <c r="D49">
-        <v>7340</v>
-      </c>
-      <c r="E49">
-        <v>13327</v>
+        <v>7405</v>
       </c>
       <c r="H49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I49">
-        <v>3.32</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>246</v>
+        <v>3726</v>
       </c>
       <c r="B50">
-        <v>1372</v>
+        <v>6673</v>
       </c>
       <c r="C50">
-        <v>5291</v>
-      </c>
-      <c r="D50">
-        <v>5554</v>
-      </c>
-      <c r="E50">
-        <v>8155</v>
-      </c>
-      <c r="F50">
-        <v>9515</v>
+        <v>8178</v>
       </c>
       <c r="H50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I50">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>6441</v>
+        <v>3007</v>
       </c>
       <c r="B51">
-        <v>7521</v>
-      </c>
-      <c r="C51">
-        <v>7790</v>
-      </c>
-      <c r="D51">
-        <v>8679</v>
-      </c>
-      <c r="E51">
-        <v>9833</v>
+        <v>8162</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>3.83</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>2677</v>
-      </c>
-      <c r="B52">
-        <v>11432</v>
+        <v>7288</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>3.54</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>3390</v>
+        <v>3399</v>
       </c>
       <c r="B53">
-        <v>5419</v>
+        <v>6332</v>
       </c>
       <c r="C53">
-        <v>11730</v>
+        <v>6686</v>
       </c>
       <c r="H53">
         <v>3</v>
       </c>
       <c r="I53">
-        <v>2.5099999999999998</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>4602</v>
-      </c>
-      <c r="B54">
-        <v>8422</v>
-      </c>
-      <c r="C54">
-        <v>9054</v>
+        <v>8675</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>2.93</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>8356</v>
-      </c>
-      <c r="B55">
-        <v>14814</v>
+        <v>8717</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55">
-        <v>4.7699999999999996</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>2286</v>
-      </c>
-      <c r="B56">
-        <v>6469</v>
-      </c>
-      <c r="C56">
-        <v>7680</v>
-      </c>
-      <c r="D56">
-        <v>9010</v>
+        <v>9530</v>
       </c>
       <c r="H56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>2769</v>
+        <v>5523</v>
       </c>
       <c r="B57">
-        <v>5005</v>
+        <v>7117</v>
       </c>
       <c r="C57">
-        <v>6536</v>
-      </c>
-      <c r="D57">
-        <v>11915</v>
+        <v>7175</v>
       </c>
       <c r="H57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I57">
-        <v>5.31</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>8125</v>
+        <v>5973</v>
       </c>
       <c r="B58">
-        <v>14548</v>
+        <v>6904</v>
+      </c>
+      <c r="C58">
+        <v>7897</v>
+      </c>
+      <c r="D58">
+        <v>8628</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I58">
-        <v>5.19</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>1928</v>
+        <v>2351</v>
       </c>
       <c r="B59">
-        <v>6359</v>
+        <v>4997</v>
       </c>
       <c r="C59">
-        <v>7303</v>
+        <v>7606</v>
       </c>
       <c r="D59">
-        <v>11262</v>
+        <v>7668</v>
+      </c>
+      <c r="E59">
+        <v>7920</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I59">
-        <v>4.74</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>15030</v>
+        <v>6145</v>
+      </c>
+      <c r="B60">
+        <v>6244</v>
+      </c>
+      <c r="C60">
+        <v>7094</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>4.1399999999999997</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>1016</v>
+        <v>2777</v>
       </c>
       <c r="B61">
-        <v>11705</v>
+        <v>6967</v>
       </c>
       <c r="H61">
         <v>2</v>
       </c>
       <c r="I61">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>4626</v>
+        <v>1179</v>
       </c>
       <c r="B62">
-        <v>6554</v>
+        <v>4399</v>
       </c>
       <c r="C62">
-        <v>9710</v>
+        <v>5640</v>
+      </c>
+      <c r="D62">
+        <v>6708</v>
+      </c>
+      <c r="E62">
+        <v>7627</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I62">
-        <v>2.72</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>1398</v>
-      </c>
-      <c r="B63">
-        <v>9330</v>
+        <v>12276</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>5405</v>
+        <v>5111</v>
       </c>
       <c r="B64">
-        <v>8771</v>
+        <v>6181</v>
       </c>
       <c r="H64">
         <v>2</v>
       </c>
       <c r="I64">
-        <v>4.83</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>438</v>
+        <v>3865</v>
       </c>
       <c r="B65">
-        <v>1700</v>
-      </c>
-      <c r="C65">
-        <v>11674</v>
+        <v>7562</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I65">
-        <v>4.3099999999999996</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>1094</v>
+        <v>2017</v>
       </c>
       <c r="B66">
-        <v>12733</v>
+        <v>2428</v>
+      </c>
+      <c r="C66">
+        <v>7100</v>
+      </c>
+      <c r="D66">
+        <v>7403</v>
       </c>
       <c r="H66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>6.63</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>9392</v>
+        <v>11588</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67">
-        <v>3.19</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>2493</v>
-      </c>
-      <c r="B68">
-        <v>13476</v>
+        <v>4393</v>
       </c>
       <c r="H68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I68">
-        <v>2.97</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>2204</v>
+        <v>1867</v>
       </c>
       <c r="B69">
-        <v>12609</v>
+        <v>7607</v>
+      </c>
+      <c r="C69">
+        <v>8183</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69">
-        <v>7.43</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>2945</v>
+        <v>1640</v>
       </c>
       <c r="B70">
-        <v>5650</v>
+        <v>5168</v>
       </c>
       <c r="C70">
-        <v>8455</v>
+        <v>5410</v>
       </c>
       <c r="D70">
-        <v>8881</v>
+        <v>5905</v>
       </c>
       <c r="H70">
         <v>4</v>
       </c>
       <c r="I70">
-        <v>4.7</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>9235</v>
+        <v>12441</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71">
-        <v>2.33</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>4681</v>
-      </c>
-      <c r="B72">
-        <v>7601</v>
-      </c>
-      <c r="C72">
-        <v>10542</v>
+        <v>12692</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>6.03</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>8829</v>
+        <v>2962</v>
+      </c>
+      <c r="B73">
+        <v>8123</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <v>3.48</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>1199</v>
-      </c>
-      <c r="B74">
-        <v>3047</v>
-      </c>
-      <c r="C74">
-        <v>4611</v>
-      </c>
-      <c r="D74">
-        <v>10584</v>
+        <v>11288</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I74">
-        <v>4.9000000000000004</v>
+        <v>4.4400000000000004</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>1024</v>
+        <v>7609</v>
       </c>
       <c r="B75">
-        <v>5793</v>
-      </c>
-      <c r="C75">
-        <v>6339</v>
-      </c>
-      <c r="D75">
-        <v>9833</v>
+        <v>7662</v>
       </c>
       <c r="H75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>2.2000000000000002</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>12149</v>
+        <v>6385</v>
+      </c>
+      <c r="B76">
+        <v>7733</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>2.97</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>2622</v>
-      </c>
-      <c r="B77">
-        <v>16131</v>
+        <v>8585</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>3309</v>
+        <v>2527</v>
       </c>
       <c r="B78">
-        <v>9115</v>
+        <v>7043</v>
+      </c>
+      <c r="C78">
+        <v>7074</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I78">
-        <v>4.33</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>1863</v>
+        <v>1126</v>
       </c>
       <c r="B79">
-        <v>2972</v>
-      </c>
-      <c r="C79">
-        <v>6419</v>
-      </c>
-      <c r="D79">
-        <v>9421</v>
+        <v>4028</v>
       </c>
       <c r="H79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I79">
-        <v>2.69</v>
+        <v>4.9800000000000004</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>3430</v>
+        <v>4931</v>
       </c>
       <c r="B80">
-        <v>13000</v>
+        <v>6338</v>
       </c>
       <c r="H80">
         <v>2</v>
       </c>
       <c r="I80">
-        <v>3.31</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>10468</v>
+        <v>8549</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>6542</v>
+        <v>4173</v>
       </c>
       <c r="B82">
-        <v>11394</v>
+        <v>5101</v>
       </c>
       <c r="H82">
         <v>2</v>
       </c>
       <c r="I82">
-        <v>3.08</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>21333</v>
+        <v>5631</v>
+      </c>
+      <c r="B83">
+        <v>7080</v>
       </c>
       <c r="H83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I83">
-        <v>4</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>12190</v>
+        <v>12439</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84">
-        <v>3.92</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>8055</v>
+        <v>1558</v>
       </c>
       <c r="B85">
-        <v>19674</v>
+        <v>7151</v>
       </c>
       <c r="H85">
         <v>2</v>
       </c>
       <c r="I85">
-        <v>3.23</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86">
-        <v>2509</v>
-      </c>
-      <c r="B86">
-        <v>9259</v>
+        <v>1905</v>
       </c>
       <c r="H86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86">
-        <v>5.18</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>9399</v>
+        <v>4065</v>
+      </c>
+      <c r="B87">
+        <v>7850</v>
+      </c>
+      <c r="C87">
+        <v>7966</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I87">
-        <v>4.58</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88">
-        <v>1512</v>
+        <v>2454</v>
       </c>
       <c r="B88">
-        <v>7866</v>
+        <v>3679</v>
       </c>
       <c r="C88">
-        <v>25441</v>
+        <v>6293</v>
+      </c>
+      <c r="D88">
+        <v>6731</v>
+      </c>
+      <c r="E88">
+        <v>7328</v>
       </c>
       <c r="H88">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I88">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89">
-        <v>7484</v>
+        <v>5015</v>
       </c>
       <c r="B89">
-        <v>16022</v>
+        <v>6815</v>
       </c>
       <c r="H89">
         <v>2</v>
       </c>
       <c r="I89">
-        <v>3.27</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90">
-        <v>1973</v>
+        <v>3890</v>
       </c>
       <c r="B90">
-        <v>6596</v>
+        <v>4655</v>
       </c>
       <c r="C90">
-        <v>8456</v>
-      </c>
-      <c r="D90">
-        <v>8591</v>
-      </c>
-      <c r="E90">
-        <v>9522</v>
+        <v>6654</v>
       </c>
       <c r="H90">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I90">
-        <v>3.85</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91">
-        <v>4163</v>
+        <v>6226</v>
       </c>
       <c r="B91">
-        <v>11197</v>
+        <v>6773</v>
       </c>
       <c r="H91">
         <v>2</v>
       </c>
       <c r="I91">
-        <v>3.78</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92">
-        <v>1435</v>
-      </c>
-      <c r="B92">
-        <v>3941</v>
-      </c>
-      <c r="C92">
-        <v>12409</v>
+        <v>4332</v>
       </c>
       <c r="H92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I92">
-        <v>4.1399999999999997</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93">
-        <v>5368</v>
+        <v>8231</v>
       </c>
       <c r="B93">
-        <v>16452</v>
+        <v>8712</v>
       </c>
       <c r="H93">
         <v>2</v>
       </c>
       <c r="I93">
-        <v>3.02</v>
+        <v>4.0599999999999996</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94">
-        <v>3764</v>
-      </c>
-      <c r="B94">
-        <v>13496</v>
+        <v>5305</v>
       </c>
       <c r="H94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I94">
-        <v>6.54</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95">
-        <v>8600</v>
+        <v>563</v>
       </c>
       <c r="B95">
-        <v>16395</v>
+        <v>5743</v>
       </c>
       <c r="H95">
         <v>2</v>
       </c>
       <c r="I95">
-        <v>4.01</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96">
-        <v>4644</v>
+        <v>4510</v>
       </c>
       <c r="B96">
-        <v>4688</v>
+        <v>5270</v>
       </c>
       <c r="C96">
-        <v>6788</v>
-      </c>
-      <c r="D96">
-        <v>9556</v>
+        <v>5622</v>
       </c>
       <c r="H96">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I96">
-        <v>4.25</v>
+        <v>4.2300000000000004</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97">
-        <v>5096</v>
+        <v>4147</v>
       </c>
       <c r="B97">
-        <v>6143</v>
-      </c>
-      <c r="C97">
-        <v>9501</v>
+        <v>7434</v>
       </c>
       <c r="H97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I97">
-        <v>3.81</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98">
-        <v>4832</v>
+        <v>2953</v>
       </c>
       <c r="B98">
-        <v>16365</v>
+        <v>7840</v>
       </c>
       <c r="H98">
         <v>2</v>
       </c>
       <c r="I98">
-        <v>2.67</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99">
-        <v>5217</v>
-      </c>
-      <c r="B99">
-        <v>13529</v>
+        <v>5303</v>
       </c>
       <c r="H99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99">
-        <v>5.14</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100">
-        <v>7356</v>
+        <v>2266</v>
       </c>
       <c r="B100">
-        <v>9108</v>
+        <v>2444</v>
+      </c>
+      <c r="C100">
+        <v>4685</v>
+      </c>
+      <c r="D100">
+        <v>5332</v>
       </c>
       <c r="H100">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I100">
-        <v>6.09</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101">
-        <v>9112</v>
+        <v>7686</v>
       </c>
       <c r="H101">
         <v>1</v>
       </c>
       <c r="I101">
-        <v>4.17</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102">
-        <v>5683</v>
+        <v>3213</v>
       </c>
       <c r="B102">
-        <v>6893</v>
-      </c>
-      <c r="C102">
-        <v>8434</v>
-      </c>
-      <c r="D102">
-        <v>15300</v>
+        <v>6840</v>
       </c>
       <c r="H102">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I102">
-        <v>3.97</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>680</v>
-      </c>
-      <c r="B103">
-        <v>1296</v>
-      </c>
-      <c r="C103">
-        <v>11320</v>
+        <v>7891</v>
       </c>
       <c r="H103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I103">
-        <v>3.19</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>4179</v>
+        <v>3940</v>
       </c>
       <c r="B104">
-        <v>4508</v>
+        <v>4681</v>
       </c>
       <c r="C104">
-        <v>16265</v>
+        <v>5659</v>
       </c>
       <c r="H104">
         <v>3</v>
       </c>
       <c r="I104">
-        <v>5.76</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>6255</v>
-      </c>
-      <c r="B105">
-        <v>8099</v>
-      </c>
-      <c r="C105">
-        <v>10533</v>
+        <v>722</v>
       </c>
       <c r="H105">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I105">
-        <v>2.25</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>2245</v>
-      </c>
-      <c r="B106">
-        <v>4162</v>
-      </c>
-      <c r="C106">
-        <v>7126</v>
-      </c>
-      <c r="D106">
-        <v>8912</v>
+        <v>2147</v>
       </c>
       <c r="H106">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I106">
-        <v>5.69</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>15820</v>
+        <v>4159</v>
+      </c>
+      <c r="B107">
+        <v>4984</v>
+      </c>
+      <c r="C107">
+        <v>5936</v>
+      </c>
+      <c r="D107">
+        <v>7350</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I107">
-        <v>3.54</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108">
-        <v>10582</v>
+        <v>10636</v>
       </c>
       <c r="H108">
         <v>1</v>
       </c>
       <c r="I108">
-        <v>4.59</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109">
-        <v>647</v>
-      </c>
-      <c r="B109">
-        <v>9460</v>
+        <v>18379</v>
       </c>
       <c r="H109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I109">
-        <v>6.95</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110">
-        <v>2955</v>
-      </c>
-      <c r="B110">
-        <v>5075</v>
-      </c>
-      <c r="C110">
-        <v>6651</v>
-      </c>
-      <c r="D110">
-        <v>6773</v>
-      </c>
-      <c r="E110">
-        <v>13668</v>
+        <v>4010</v>
       </c>
       <c r="H110">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I110">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111">
-        <v>2963</v>
-      </c>
-      <c r="B111">
-        <v>5460</v>
-      </c>
-      <c r="C111">
-        <v>9792</v>
+        <v>3273</v>
       </c>
       <c r="H111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I111">
-        <v>5.32</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112">
-        <v>2782</v>
+        <v>6224</v>
       </c>
       <c r="B112">
-        <v>4744</v>
-      </c>
-      <c r="C112">
-        <v>4990</v>
-      </c>
-      <c r="D112">
-        <v>5156</v>
-      </c>
-      <c r="E112">
-        <v>6750</v>
-      </c>
-      <c r="F112">
-        <v>7633</v>
-      </c>
-      <c r="G112">
-        <v>11112</v>
+        <v>8579</v>
       </c>
       <c r="H112">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I112">
-        <v>6.16</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113">
-        <v>9596</v>
+        <v>1019</v>
+      </c>
+      <c r="B113">
+        <v>7748</v>
       </c>
       <c r="H113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I113">
-        <v>5.19</v>
+        <v>4.3600000000000003</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114">
-        <v>3159</v>
-      </c>
-      <c r="B114">
-        <v>5946</v>
-      </c>
-      <c r="C114">
-        <v>6873</v>
-      </c>
-      <c r="D114">
-        <v>8329</v>
-      </c>
-      <c r="E114">
-        <v>10734</v>
+        <v>2993</v>
       </c>
       <c r="H114">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I114">
-        <v>3.99</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115">
-        <v>6445</v>
-      </c>
-      <c r="B115">
-        <v>10442</v>
+        <v>3857</v>
       </c>
       <c r="H115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I115">
-        <v>4.9400000000000004</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116">
-        <v>8252</v>
+        <v>4164</v>
       </c>
       <c r="B116">
-        <v>10181</v>
+        <v>6978</v>
+      </c>
+      <c r="C116">
+        <v>8460</v>
       </c>
       <c r="H116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I116">
-        <v>6.24</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117">
-        <v>3838</v>
+        <v>5734</v>
       </c>
       <c r="B117">
-        <v>8810</v>
+        <v>8719</v>
       </c>
       <c r="H117">
         <v>2</v>
       </c>
       <c r="I117">
-        <v>5.24</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118">
-        <v>2552</v>
+        <v>2746</v>
       </c>
       <c r="B118">
-        <v>9614</v>
+        <v>3026</v>
       </c>
       <c r="H118">
         <v>2</v>
       </c>
       <c r="I118">
-        <v>4.18</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119">
-        <v>7113</v>
-      </c>
-      <c r="B119">
-        <v>9508</v>
+        <v>6323</v>
       </c>
       <c r="H119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I119">
-        <v>3.77</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120">
-        <v>4395</v>
-      </c>
-      <c r="B120">
-        <v>5181</v>
-      </c>
-      <c r="C120">
-        <v>6166</v>
-      </c>
-      <c r="D120">
-        <v>9203</v>
+        <v>10610</v>
       </c>
       <c r="H120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I120">
-        <v>4.26</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121">
-        <v>2762</v>
-      </c>
-      <c r="B121">
-        <v>7349</v>
-      </c>
-      <c r="C121">
-        <v>14255</v>
+        <v>4715</v>
       </c>
       <c r="H121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I121">
-        <v>4.18</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122">
-        <v>299</v>
-      </c>
-      <c r="B122">
-        <v>2454</v>
-      </c>
-      <c r="C122">
-        <v>4986</v>
-      </c>
-      <c r="D122">
-        <v>6486</v>
-      </c>
-      <c r="E122">
-        <v>8772</v>
+        <v>12032</v>
       </c>
       <c r="H122">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I122">
-        <v>4.43</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>10932</v>
+        <v>7710</v>
+      </c>
+      <c r="B123">
+        <v>8487</v>
       </c>
       <c r="H123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I123">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>6048</v>
+        <v>4571</v>
       </c>
       <c r="B124">
-        <v>6942</v>
+        <v>5655</v>
       </c>
       <c r="C124">
-        <v>12577</v>
+        <v>6355</v>
       </c>
       <c r="H124">
         <v>3</v>
       </c>
       <c r="I124">
-        <v>6.17</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125">
-        <v>6225</v>
+        <v>7027</v>
       </c>
       <c r="B125">
-        <v>8209</v>
-      </c>
-      <c r="C125">
-        <v>12124</v>
+        <v>8430</v>
       </c>
       <c r="H125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I125">
-        <v>4.9400000000000004</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126">
-        <v>477</v>
+        <v>531</v>
       </c>
       <c r="B126">
-        <v>2496</v>
+        <v>5821</v>
       </c>
       <c r="C126">
-        <v>7368</v>
-      </c>
-      <c r="D126">
-        <v>10250</v>
+        <v>5839</v>
       </c>
       <c r="H126">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I126">
-        <v>2.97</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127">
-        <v>3691</v>
-      </c>
-      <c r="B127">
-        <v>8943</v>
+        <v>1836</v>
       </c>
       <c r="H127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I127">
-        <v>4.95</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128">
-        <v>6022</v>
-      </c>
-      <c r="B128">
-        <v>6466</v>
-      </c>
-      <c r="C128">
-        <v>7030</v>
-      </c>
-      <c r="D128">
-        <v>9161</v>
+        <v>11284</v>
       </c>
       <c r="H128">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I128">
-        <v>3.47</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129">
-        <v>3107</v>
-      </c>
-      <c r="B129">
-        <v>9098</v>
+        <v>5283</v>
       </c>
       <c r="H129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I129">
-        <v>5.31</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130">
-        <v>910</v>
+        <v>3342</v>
       </c>
       <c r="B130">
-        <v>10858</v>
+        <v>3751</v>
+      </c>
+      <c r="C130">
+        <v>7324</v>
+      </c>
+      <c r="D130">
+        <v>8055</v>
       </c>
       <c r="H130">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I130">
-        <v>3.58</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131">
-        <v>988</v>
+        <v>2109</v>
       </c>
       <c r="B131">
-        <v>5907</v>
+        <v>6649</v>
       </c>
       <c r="C131">
-        <v>6796</v>
-      </c>
-      <c r="D131">
-        <v>16102</v>
+        <v>6677</v>
       </c>
       <c r="H131">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I131">
-        <v>3.52</v>
+        <v>4.4800000000000004</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>11171</v>
+        <v>4062</v>
       </c>
       <c r="H132">
         <v>1</v>
       </c>
       <c r="I132">
-        <v>2.19</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133">
-        <v>1140</v>
-      </c>
-      <c r="B133">
-        <v>4387</v>
-      </c>
-      <c r="C133">
-        <v>9691</v>
+        <v>857</v>
       </c>
       <c r="H133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I133">
-        <v>5</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>2899</v>
-      </c>
-      <c r="B134">
-        <v>7842</v>
-      </c>
-      <c r="C134">
-        <v>9320</v>
+        <v>6273</v>
       </c>
       <c r="H134">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I134">
-        <v>5.38</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>900</v>
-      </c>
-      <c r="B135">
-        <v>1626</v>
-      </c>
-      <c r="C135">
-        <v>2591</v>
-      </c>
-      <c r="D135">
-        <v>12384</v>
+        <v>9812</v>
       </c>
       <c r="H135">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I135">
-        <v>5.1100000000000003</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>1252</v>
-      </c>
-      <c r="B136">
-        <v>3639</v>
-      </c>
-      <c r="C136">
-        <v>10913</v>
+        <v>8027</v>
       </c>
       <c r="H136">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I136">
-        <v>4.7699999999999996</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137">
-        <v>4032</v>
-      </c>
-      <c r="B137">
-        <v>15818</v>
+        <v>15446</v>
       </c>
       <c r="H137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I137">
-        <v>3.22</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138">
-        <v>1504</v>
+        <v>2237</v>
       </c>
       <c r="B138">
-        <v>4877</v>
+        <v>5930</v>
       </c>
       <c r="C138">
-        <v>5439</v>
+        <v>6248</v>
       </c>
       <c r="D138">
-        <v>6317</v>
-      </c>
-      <c r="E138">
-        <v>7903</v>
-      </c>
-      <c r="F138">
-        <v>11095</v>
+        <v>8431</v>
       </c>
       <c r="H138">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I138">
-        <v>4.5599999999999996</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139">
-        <v>933</v>
+        <v>2845</v>
       </c>
       <c r="B139">
-        <v>5962</v>
+        <v>6237</v>
       </c>
       <c r="C139">
-        <v>9023</v>
+        <v>8738</v>
       </c>
       <c r="H139">
         <v>3</v>
       </c>
       <c r="I139">
-        <v>4.1500000000000004</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140">
-        <v>10499</v>
+        <v>7051</v>
       </c>
       <c r="H140">
         <v>1</v>
       </c>
       <c r="I140">
-        <v>3.07</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141">
-        <v>1428</v>
+        <v>542</v>
       </c>
       <c r="B141">
-        <v>2298</v>
+        <v>736</v>
       </c>
       <c r="C141">
-        <v>7787</v>
+        <v>4226</v>
       </c>
       <c r="D141">
-        <v>10353</v>
+        <v>4621</v>
+      </c>
+      <c r="E141">
+        <v>4857</v>
+      </c>
+      <c r="F141">
+        <v>5431</v>
+      </c>
+      <c r="G141">
+        <v>7284</v>
       </c>
       <c r="H141">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I141">
-        <v>2.69</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142">
-        <v>451</v>
-      </c>
-      <c r="B142">
-        <v>8469</v>
-      </c>
-      <c r="C142">
-        <v>16370</v>
+        <v>7323</v>
       </c>
       <c r="H142">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I142">
-        <v>3.33</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143">
-        <v>9275</v>
+        <v>5153</v>
       </c>
       <c r="H143">
         <v>1</v>
       </c>
       <c r="I143">
-        <v>2.3199999999999998</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144">
-        <v>1675</v>
+        <v>3410</v>
       </c>
       <c r="B144">
-        <v>1717</v>
-      </c>
-      <c r="C144">
-        <v>10210</v>
+        <v>5726</v>
       </c>
       <c r="H144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I144">
-        <v>4.26</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>3464</v>
+        <v>2058</v>
       </c>
       <c r="B145">
-        <v>6620</v>
+        <v>8311</v>
       </c>
       <c r="C145">
-        <v>11043</v>
+        <v>8631</v>
       </c>
       <c r="H145">
         <v>3</v>
       </c>
       <c r="I145">
-        <v>3.13</v>
+        <v>4.3899999999999997</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146">
-        <v>7032</v>
-      </c>
-      <c r="B146">
-        <v>9743</v>
+        <v>4279</v>
       </c>
       <c r="H146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I146">
-        <v>3.68</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147">
-        <v>4014</v>
+        <v>1785</v>
       </c>
       <c r="B147">
-        <v>16329</v>
+        <v>3070</v>
       </c>
       <c r="H147">
         <v>2</v>
       </c>
       <c r="I147">
-        <v>3.59</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148">
-        <v>2122</v>
-      </c>
-      <c r="B148">
-        <v>13221</v>
+        <v>1120</v>
       </c>
       <c r="H148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I148">
-        <v>4.07</v>
+        <v>4.0599999999999996</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149">
-        <v>998</v>
-      </c>
-      <c r="B149">
-        <v>1301</v>
-      </c>
-      <c r="C149">
-        <v>4939</v>
-      </c>
-      <c r="D149">
-        <v>9549</v>
+        <v>6695</v>
       </c>
       <c r="H149">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I149">
-        <v>3.85</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150">
-        <v>5227</v>
+        <v>4176</v>
       </c>
       <c r="B150">
-        <v>9492</v>
+        <v>6432</v>
       </c>
       <c r="H150">
         <v>2</v>
       </c>
       <c r="I150">
-        <v>3.87</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151">
-        <v>3021</v>
-      </c>
-      <c r="B151">
-        <v>4274</v>
-      </c>
-      <c r="C151">
-        <v>5563</v>
-      </c>
-      <c r="D151">
-        <v>5578</v>
-      </c>
-      <c r="E151">
-        <v>18297</v>
+        <v>9141</v>
       </c>
       <c r="H151">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I151">
-        <v>2.67</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152">
-        <v>4353</v>
+        <v>6326</v>
       </c>
       <c r="B152">
-        <v>5181</v>
+        <v>6908</v>
       </c>
       <c r="C152">
-        <v>6510</v>
-      </c>
-      <c r="D152">
-        <v>9508</v>
+        <v>6956</v>
       </c>
       <c r="H152">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I152">
-        <v>3.49</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153">
-        <v>9704</v>
+        <v>2600</v>
+      </c>
+      <c r="B153">
+        <v>2936</v>
+      </c>
+      <c r="C153">
+        <v>8434</v>
       </c>
       <c r="H153">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I153">
-        <v>3.81</v>
+        <v>4.1399999999999997</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154">
-        <v>13138</v>
+        <v>8893</v>
       </c>
       <c r="H154">
         <v>1</v>
       </c>
       <c r="I154">
-        <v>2.89</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155">
-        <v>1104</v>
+        <v>4277</v>
       </c>
       <c r="B155">
-        <v>3477</v>
+        <v>6341</v>
       </c>
       <c r="C155">
-        <v>9281</v>
+        <v>8417</v>
       </c>
       <c r="H155">
         <v>3</v>
       </c>
       <c r="I155">
-        <v>5.6</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156">
-        <v>4390</v>
-      </c>
-      <c r="B156">
-        <v>6869</v>
-      </c>
-      <c r="C156">
-        <v>12888</v>
+        <v>9808</v>
       </c>
       <c r="H156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I156">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157">
-        <v>3817</v>
-      </c>
-      <c r="B157">
-        <v>7594</v>
-      </c>
-      <c r="C157">
-        <v>8680</v>
-      </c>
-      <c r="D157">
-        <v>15720</v>
+        <v>6281</v>
       </c>
       <c r="H157">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I157">
-        <v>4.7300000000000004</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158">
-        <v>1484</v>
-      </c>
-      <c r="B158">
-        <v>6129</v>
-      </c>
-      <c r="C158">
-        <v>7791</v>
-      </c>
-      <c r="D158">
-        <v>15206</v>
+        <v>11063</v>
       </c>
       <c r="H158">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I158">
-        <v>2.56</v>
+        <v>4.6500000000000004</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159">
-        <v>6182</v>
+        <v>3229</v>
       </c>
       <c r="B159">
-        <v>6950</v>
+        <v>4418</v>
       </c>
       <c r="C159">
-        <v>10128</v>
+        <v>4789</v>
+      </c>
+      <c r="D159">
+        <v>7884</v>
       </c>
       <c r="H159">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I159">
-        <v>2.68</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160">
-        <v>1872</v>
+        <v>4775</v>
       </c>
       <c r="B160">
-        <v>6293</v>
-      </c>
-      <c r="C160">
-        <v>11383</v>
+        <v>5316</v>
       </c>
       <c r="H160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I160">
-        <v>2.38</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161">
-        <v>2604</v>
-      </c>
-      <c r="B161">
-        <v>7315</v>
-      </c>
-      <c r="C161">
-        <v>9891</v>
+        <v>5659</v>
       </c>
       <c r="H161">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I161">
-        <v>2.27</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162">
-        <v>5686</v>
-      </c>
-      <c r="B162">
-        <v>7092</v>
-      </c>
-      <c r="C162">
-        <v>7583</v>
-      </c>
-      <c r="D162">
-        <v>10552</v>
+        <v>3567</v>
       </c>
       <c r="H162">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I162">
-        <v>2.57</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163">
-        <v>1983</v>
+        <v>2073</v>
       </c>
       <c r="B163">
-        <v>2315</v>
+        <v>3649</v>
       </c>
       <c r="C163">
-        <v>2818</v>
+        <v>4883</v>
       </c>
       <c r="D163">
-        <v>4242</v>
-      </c>
-      <c r="E163">
-        <v>8537</v>
-      </c>
-      <c r="F163">
-        <v>11880</v>
+        <v>8597</v>
       </c>
       <c r="H163">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I163">
-        <v>3.18</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164">
-        <v>6977</v>
-      </c>
-      <c r="B164">
-        <v>14600</v>
+        <v>8878</v>
       </c>
       <c r="H164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I164">
-        <v>3.9</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165">
-        <v>793</v>
-      </c>
-      <c r="B165">
-        <v>9042</v>
+        <v>2895</v>
       </c>
       <c r="H165">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I165">
-        <v>3.3</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166">
-        <v>8624</v>
+        <v>2924</v>
       </c>
       <c r="B166">
-        <v>10900</v>
+        <v>5705</v>
+      </c>
+      <c r="C166">
+        <v>6150</v>
+      </c>
+      <c r="D166">
+        <v>6894</v>
+      </c>
+      <c r="E166">
+        <v>6968</v>
       </c>
       <c r="H166">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I166">
-        <v>5.14</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167">
-        <v>8800</v>
+        <v>3547</v>
+      </c>
+      <c r="B167">
+        <v>5960</v>
       </c>
       <c r="H167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I167">
-        <v>2.13</v>
+        <v>4.9800000000000004</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168">
-        <v>8456</v>
+        <v>5100</v>
       </c>
       <c r="B168">
-        <v>8950</v>
+        <v>6690</v>
+      </c>
+      <c r="C168">
+        <v>6696</v>
+      </c>
+      <c r="D168">
+        <v>8361</v>
       </c>
       <c r="H168">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I168">
-        <v>5.23</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169">
-        <v>1118</v>
+        <v>3268</v>
       </c>
       <c r="B169">
-        <v>3005</v>
-      </c>
-      <c r="C169">
-        <v>9406</v>
+        <v>5695</v>
       </c>
       <c r="H169">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I169">
-        <v>4.2300000000000004</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170">
-        <v>2778</v>
+        <v>3262</v>
       </c>
       <c r="B170">
-        <v>15466</v>
+        <v>6344</v>
       </c>
       <c r="H170">
         <v>2</v>
       </c>
       <c r="I170">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171">
-        <v>807</v>
+        <v>3781</v>
       </c>
       <c r="B171">
-        <v>5050</v>
+        <v>4773</v>
       </c>
       <c r="C171">
-        <v>12798</v>
+        <v>7975</v>
       </c>
       <c r="H171">
         <v>3</v>
       </c>
       <c r="I171">
-        <v>3.98</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172">
-        <v>3410</v>
+        <v>3766</v>
       </c>
       <c r="B172">
-        <v>10545</v>
+        <v>5308</v>
+      </c>
+      <c r="C172">
+        <v>7926</v>
       </c>
       <c r="H172">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I172">
-        <v>3.47</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173">
-        <v>4635</v>
+        <v>2873</v>
       </c>
       <c r="B173">
-        <v>7051</v>
+        <v>5326</v>
       </c>
       <c r="C173">
-        <v>7585</v>
+        <v>8011</v>
       </c>
       <c r="D173">
-        <v>11356</v>
+        <v>8509</v>
       </c>
       <c r="H173">
         <v>4</v>
       </c>
       <c r="I173">
-        <v>2.17</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174">
-        <v>7975</v>
-      </c>
-      <c r="B174">
-        <v>12456</v>
+        <v>11480</v>
       </c>
       <c r="H174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I174">
-        <v>4.04</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175">
-        <v>7835</v>
-      </c>
-      <c r="B175">
-        <v>17493</v>
+        <v>6614</v>
       </c>
       <c r="H175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I175">
-        <v>5.1100000000000003</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176">
-        <v>3113</v>
-      </c>
-      <c r="B176">
-        <v>3671</v>
-      </c>
-      <c r="C176">
-        <v>4351</v>
-      </c>
-      <c r="D176">
-        <v>17142</v>
+        <v>3030</v>
       </c>
       <c r="H176">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I176">
-        <v>3.52</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177">
-        <v>3891</v>
-      </c>
-      <c r="B177">
-        <v>8376</v>
-      </c>
-      <c r="C177">
-        <v>9656</v>
+        <v>5860</v>
       </c>
       <c r="H177">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I177">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178">
-        <v>2571</v>
+        <v>1045</v>
       </c>
       <c r="B178">
-        <v>8098</v>
+        <v>3051</v>
       </c>
       <c r="C178">
-        <v>10303</v>
+        <v>3650</v>
+      </c>
+      <c r="D178">
+        <v>8302</v>
       </c>
       <c r="H178">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I178">
-        <v>3.67</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179">
-        <v>8664</v>
-      </c>
-      <c r="B179">
-        <v>8724</v>
-      </c>
-      <c r="C179">
-        <v>11401</v>
+        <v>10254</v>
       </c>
       <c r="H179">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I179">
-        <v>4.62</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180">
-        <v>4210</v>
-      </c>
-      <c r="B180">
-        <v>7447</v>
-      </c>
-      <c r="C180">
-        <v>8152</v>
-      </c>
-      <c r="D180">
-        <v>13724</v>
+        <v>5552</v>
       </c>
       <c r="H180">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I180">
-        <v>3.89</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181">
-        <v>6496</v>
+        <v>3419</v>
       </c>
       <c r="B181">
-        <v>9360</v>
+        <v>5124</v>
       </c>
       <c r="H181">
         <v>2</v>
       </c>
       <c r="I181">
-        <v>3.42</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182">
-        <v>5645</v>
-      </c>
-      <c r="B182">
-        <v>6819</v>
-      </c>
-      <c r="C182">
-        <v>19644</v>
+        <v>9086</v>
       </c>
       <c r="H182">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I182">
-        <v>3.81</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183">
-        <v>4197</v>
-      </c>
-      <c r="B183">
-        <v>7771</v>
-      </c>
-      <c r="C183">
-        <v>9588</v>
+        <v>13076</v>
       </c>
       <c r="H183">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I183">
-        <v>3.93</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184">
-        <v>5053</v>
+        <v>1709</v>
       </c>
       <c r="B184">
-        <v>6754</v>
-      </c>
-      <c r="C184">
-        <v>8467</v>
-      </c>
-      <c r="D184">
-        <v>27821</v>
+        <v>7851</v>
       </c>
       <c r="H184">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I184">
-        <v>2.62</v>
+        <v>4.9800000000000004</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185">
-        <v>1815</v>
+        <v>1004</v>
       </c>
       <c r="B185">
-        <v>11073</v>
+        <v>2447</v>
+      </c>
+      <c r="C185">
+        <v>8744</v>
       </c>
       <c r="H185">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I185">
-        <v>4.92</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186">
-        <v>1615</v>
-      </c>
-      <c r="B186">
-        <v>5543</v>
-      </c>
-      <c r="C186">
-        <v>10363</v>
+        <v>12699</v>
       </c>
       <c r="H186">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I186">
-        <v>4.71</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187">
-        <v>4799</v>
+        <v>403</v>
       </c>
       <c r="B187">
-        <v>7414</v>
+        <v>3204</v>
       </c>
       <c r="C187">
-        <v>10434</v>
+        <v>6235</v>
+      </c>
+      <c r="D187">
+        <v>8191</v>
       </c>
       <c r="H187">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I187">
-        <v>2.9</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188">
-        <v>3966</v>
-      </c>
-      <c r="B188">
-        <v>4557</v>
-      </c>
-      <c r="C188">
-        <v>5603</v>
-      </c>
-      <c r="D188">
-        <v>6174</v>
-      </c>
-      <c r="E188">
-        <v>18884</v>
+        <v>1330</v>
       </c>
       <c r="H188">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I188">
-        <v>2.66</v>
+        <v>4.8899999999999997</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189">
-        <v>1975</v>
-      </c>
-      <c r="B189">
-        <v>4410</v>
-      </c>
-      <c r="C189">
-        <v>11475</v>
+        <v>12266</v>
       </c>
       <c r="H189">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I189">
-        <v>5.19</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190">
-        <v>3402</v>
+        <v>4719</v>
       </c>
       <c r="B190">
-        <v>4798</v>
-      </c>
-      <c r="C190">
-        <v>10654</v>
+        <v>5218</v>
       </c>
       <c r="H190">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I190">
-        <v>6.4</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191">
-        <v>4675</v>
+        <v>1348</v>
       </c>
       <c r="B191">
-        <v>4875</v>
+        <v>1776</v>
       </c>
       <c r="C191">
-        <v>5711</v>
-      </c>
-      <c r="D191">
-        <v>6331</v>
-      </c>
-      <c r="E191">
-        <v>6760</v>
-      </c>
-      <c r="F191">
-        <v>7521</v>
-      </c>
-      <c r="G191">
-        <v>9069</v>
+        <v>6363</v>
       </c>
       <c r="H191">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I191">
-        <v>3.19</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192">
-        <v>6360</v>
+        <v>4436</v>
       </c>
       <c r="B192">
-        <v>14463</v>
+        <v>8756</v>
       </c>
       <c r="H192">
         <v>2</v>
       </c>
       <c r="I192">
-        <v>2.13</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193">
-        <v>909</v>
+        <v>956</v>
       </c>
       <c r="B193">
-        <v>5581</v>
+        <v>1547</v>
       </c>
       <c r="C193">
-        <v>12015</v>
+        <v>2590</v>
+      </c>
+      <c r="D193">
+        <v>3071</v>
+      </c>
+      <c r="E193">
+        <v>7138</v>
       </c>
       <c r="H193">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I193">
-        <v>3.17</v>
+        <v>4.1500000000000004</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194">
-        <v>3639</v>
+        <v>6093</v>
       </c>
       <c r="B194">
-        <v>3943</v>
-      </c>
-      <c r="C194">
-        <v>9533</v>
+        <v>6905</v>
       </c>
       <c r="H194">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I194">
-        <v>2.8</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195">
-        <v>644</v>
+        <v>3752</v>
       </c>
       <c r="B195">
-        <v>3033</v>
+        <v>5794</v>
       </c>
       <c r="C195">
-        <v>4389</v>
-      </c>
-      <c r="D195">
-        <v>4735</v>
-      </c>
-      <c r="E195">
-        <v>5724</v>
-      </c>
-      <c r="F195">
-        <v>6052</v>
-      </c>
-      <c r="G195">
-        <v>14662</v>
+        <v>8657</v>
       </c>
       <c r="H195">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I195">
-        <v>1.64</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196">
-        <v>12277</v>
+        <v>6033</v>
+      </c>
+      <c r="B196">
+        <v>7692</v>
       </c>
       <c r="H196">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I196">
-        <v>2.0699999999999998</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197">
-        <v>15643</v>
+        <v>2484</v>
       </c>
       <c r="H197">
         <v>1</v>
       </c>
       <c r="I197">
-        <v>4.37</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198">
-        <v>1681</v>
-      </c>
-      <c r="B198">
-        <v>2274</v>
-      </c>
-      <c r="C198">
-        <v>16855</v>
+        <v>4349</v>
       </c>
       <c r="H198">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I198">
-        <v>5.22</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199">
-        <v>4316</v>
-      </c>
-      <c r="B199">
-        <v>14620</v>
+        <v>10715</v>
       </c>
       <c r="H199">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I199">
-        <v>3.59</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200">
-        <v>6007</v>
+        <v>841</v>
       </c>
       <c r="B200">
-        <v>6283</v>
-      </c>
-      <c r="C200">
-        <v>7449</v>
-      </c>
-      <c r="D200">
-        <v>9774</v>
+        <v>5575</v>
       </c>
       <c r="H200">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I200">
-        <v>4.1100000000000003</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201">
-        <v>6302</v>
-      </c>
-      <c r="B201">
-        <v>7387</v>
-      </c>
-      <c r="C201">
-        <v>7488</v>
-      </c>
-      <c r="D201">
-        <v>10058</v>
+        <v>6868</v>
       </c>
       <c r="H201">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I201">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202">
-        <v>1333</v>
-      </c>
-      <c r="B202">
-        <v>2344</v>
-      </c>
-      <c r="C202">
-        <v>14598</v>
+        <v>12746</v>
       </c>
       <c r="H202">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I202">
-        <v>3.02</v>
+        <v>4.7699999999999996</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203">
-        <v>6667</v>
-      </c>
-      <c r="B203">
-        <v>20589</v>
+        <v>7012</v>
       </c>
       <c r="H203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I203">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204">
-        <v>5879</v>
+        <v>5855</v>
       </c>
       <c r="B204">
-        <v>6113</v>
+        <v>6759</v>
       </c>
       <c r="C204">
-        <v>7723</v>
-      </c>
-      <c r="D204">
-        <v>13220</v>
+        <v>8106</v>
       </c>
       <c r="H204">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I204">
-        <v>6.13</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205">
-        <v>10920</v>
+        <v>5220</v>
+      </c>
+      <c r="B205">
+        <v>5556</v>
       </c>
       <c r="H205">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I205">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206">
-        <v>3229</v>
+        <v>232</v>
       </c>
       <c r="B206">
-        <v>3243</v>
+        <v>3808</v>
       </c>
       <c r="C206">
-        <v>10310</v>
+        <v>6365</v>
       </c>
       <c r="H206">
         <v>3</v>
       </c>
       <c r="I206">
-        <v>2.77</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207">
-        <v>2250</v>
-      </c>
-      <c r="B207">
-        <v>3966</v>
-      </c>
-      <c r="C207">
-        <v>10549</v>
+        <v>4567</v>
       </c>
       <c r="H207">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I207">
-        <v>4.13</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208">
-        <v>12601</v>
+        <v>5826</v>
       </c>
       <c r="H208">
         <v>1</v>
       </c>
       <c r="I208">
-        <v>3.33</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209">
-        <v>6838</v>
-      </c>
-      <c r="B209">
-        <v>8193</v>
-      </c>
-      <c r="C209">
-        <v>9199</v>
+        <v>3690</v>
       </c>
       <c r="H209">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I209">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210">
-        <v>6892</v>
+        <v>7129</v>
       </c>
       <c r="B210">
-        <v>11613</v>
+        <v>7872</v>
       </c>
       <c r="H210">
         <v>2</v>
       </c>
       <c r="I210">
-        <v>4.7300000000000004</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211">
-        <v>2141</v>
+        <v>3561</v>
       </c>
       <c r="B211">
-        <v>4511</v>
+        <v>4731</v>
       </c>
       <c r="C211">
-        <v>12826</v>
+        <v>6006</v>
+      </c>
+      <c r="D211">
+        <v>6993</v>
+      </c>
+      <c r="E211">
+        <v>7493</v>
       </c>
       <c r="H211">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I211">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
     </row>
   </sheetData>
@@ -4334,7 +3881,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
@@ -6868,7 +6415,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
@@ -6880,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="3">
-        <v>-2</v>
+        <v>-1.5</v>
       </c>
     </row>
   </sheetData>
@@ -6980,7 +6527,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6992,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>-2</v>
+        <v>-1.5</v>
       </c>
     </row>
   </sheetData>
